--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260810.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2845</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>遠東銀</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>99,084,000</t>
+          <t>8,422,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>遠東銀</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>8,422,000</t>
+          <t>99,084,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>宏全</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,795,000</t>
+          <t>8,119,597</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>宏全</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>8,119,597</t>
+          <t>12,795,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>復盛應用</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,960,000</t>
+          <t>3,863,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>復盛應用</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,863,000</t>
+          <t>2,960,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
